--- a/artfynd/A 30573-2024 artfynd.xlsx
+++ b/artfynd/A 30573-2024 artfynd.xlsx
@@ -2954,10 +2954,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119537020</v>
+        <v>119536650</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2970,21 +2970,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574470</v>
+        <v>574299</v>
       </c>
       <c r="R23" t="n">
-        <v>7173208</v>
+        <v>7173057</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3066,10 +3066,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119536650</v>
+        <v>119537020</v>
       </c>
       <c r="B24" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3082,21 +3082,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574299</v>
+        <v>574470</v>
       </c>
       <c r="R24" t="n">
-        <v>7173057</v>
+        <v>7173208</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3611,10 +3611,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119536410</v>
+        <v>119536242</v>
       </c>
       <c r="B29" t="n">
-        <v>90905</v>
+        <v>90067</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3623,25 +3623,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2062</v>
+        <v>256703</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574478</v>
+        <v>574298</v>
       </c>
       <c r="R29" t="n">
-        <v>7173213</v>
+        <v>7172996</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3696,12 +3696,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>19:57</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>S. Str</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3712,21 +3707,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3972,10 +3952,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119536242</v>
+        <v>119536410</v>
       </c>
       <c r="B32" t="n">
-        <v>90067</v>
+        <v>90905</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3984,25 +3964,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>256703</v>
+        <v>2062</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4012,10 +3992,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574298</v>
+        <v>574478</v>
       </c>
       <c r="R32" t="n">
-        <v>7172996</v>
+        <v>7173213</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4047,7 +4027,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4057,7 +4037,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>S. Str</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4068,6 +4053,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4186,10 +4186,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119536704</v>
+        <v>119536396</v>
       </c>
       <c r="B34" t="n">
-        <v>90954</v>
+        <v>79608</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4202,16 +4202,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6040186</v>
+        <v>2081</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4221,10 +4226,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574517</v>
+        <v>574301</v>
       </c>
       <c r="R34" t="n">
-        <v>7173204</v>
+        <v>7173058</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4256,7 +4261,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4266,7 +4271,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4293,10 +4298,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119536396</v>
+        <v>119536704</v>
       </c>
       <c r="B35" t="n">
-        <v>79608</v>
+        <v>90954</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4309,21 +4314,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4333,10 +4333,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574301</v>
+        <v>574517</v>
       </c>
       <c r="R35" t="n">
-        <v>7173058</v>
+        <v>7173204</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 30573-2024 artfynd.xlsx
+++ b/artfynd/A 30573-2024 artfynd.xlsx
@@ -3611,10 +3611,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119536242</v>
+        <v>119536410</v>
       </c>
       <c r="B29" t="n">
-        <v>90067</v>
+        <v>90905</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3623,25 +3623,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>256703</v>
+        <v>2062</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574298</v>
+        <v>574478</v>
       </c>
       <c r="R29" t="n">
-        <v>7172996</v>
+        <v>7173213</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3696,7 +3696,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>S. Str</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3707,6 +3712,21 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3952,10 +3972,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119536410</v>
+        <v>119536242</v>
       </c>
       <c r="B32" t="n">
-        <v>90905</v>
+        <v>90067</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3964,25 +3984,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2062</v>
+        <v>256703</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3992,10 +4012,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574478</v>
+        <v>574298</v>
       </c>
       <c r="R32" t="n">
-        <v>7173213</v>
+        <v>7172996</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4027,7 +4047,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4037,12 +4057,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>19:57</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>S. Str</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4053,21 +4068,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">

--- a/artfynd/A 30573-2024 artfynd.xlsx
+++ b/artfynd/A 30573-2024 artfynd.xlsx
@@ -1116,7 +1116,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119537764</v>
+        <v>119537741</v>
       </c>
       <c r="B6" t="n">
         <v>78526</v>
@@ -1156,10 +1156,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574381</v>
+        <v>574317</v>
       </c>
       <c r="R6" t="n">
-        <v>7173062</v>
+        <v>7173030</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1218,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119537746</v>
+        <v>119536650</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1234,37 +1234,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574574</v>
+        <v>574299</v>
       </c>
       <c r="R7" t="n">
-        <v>7173271</v>
+        <v>7173057</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1288,12 +1288,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,17 +1323,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119536651</v>
+        <v>119536051</v>
       </c>
       <c r="B8" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1336,34 +1346,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574475</v>
+        <v>574493</v>
       </c>
       <c r="R8" t="n">
-        <v>7173208</v>
+        <v>7173176</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1395,7 +1410,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1405,7 +1420,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,10 +1447,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119537741</v>
+        <v>119536013</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1448,37 +1463,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574317</v>
+        <v>574482</v>
       </c>
       <c r="R9" t="n">
-        <v>7173030</v>
+        <v>7173212</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1502,12 +1517,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1527,17 +1552,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119537766</v>
+        <v>119536452</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>91852</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,41 +1571,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574395</v>
+        <v>574298</v>
       </c>
       <c r="R10" t="n">
-        <v>7173021</v>
+        <v>7172996</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1604,12 +1629,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1629,17 +1664,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119536288</v>
+        <v>119537765</v>
       </c>
       <c r="B11" t="n">
-        <v>79636</v>
+        <v>90576</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1648,41 +1683,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574304</v>
+        <v>574394</v>
       </c>
       <c r="R11" t="n">
-        <v>7173083</v>
+        <v>7173055</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1706,22 +1741,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>19:08</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>19:08</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1741,17 +1766,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119536649</v>
+        <v>119537020</v>
       </c>
       <c r="B12" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1764,21 +1789,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1788,10 +1813,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574271</v>
+        <v>574470</v>
       </c>
       <c r="R12" t="n">
-        <v>7173023</v>
+        <v>7173208</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1823,7 +1848,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1833,7 +1858,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1860,10 +1885,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119537744</v>
+        <v>119536053</v>
       </c>
       <c r="B13" t="n">
-        <v>56522</v>
+        <v>57310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,50 +1897,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vilhelmina, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574625</v>
+        <v>574455</v>
       </c>
       <c r="R13" t="n">
-        <v>7173279</v>
+        <v>7173175</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1939,12 +1960,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1964,17 +1995,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119536013</v>
+        <v>119537773</v>
       </c>
       <c r="B14" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1987,37 +2018,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574482</v>
+        <v>574368</v>
       </c>
       <c r="R14" t="n">
-        <v>7173212</v>
+        <v>7172978</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2041,22 +2072,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>19:54</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>19:54</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,14 +2097,14 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119537755</v>
+        <v>119537748</v>
       </c>
       <c r="B15" t="n">
         <v>78526</v>
@@ -2185,10 +2206,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119536511</v>
+        <v>119537769</v>
       </c>
       <c r="B16" t="n">
-        <v>90846</v>
+        <v>78526</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2201,37 +2222,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574477</v>
+        <v>574386</v>
       </c>
       <c r="R16" t="n">
-        <v>7173211</v>
+        <v>7173013</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2255,22 +2276,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>19:57</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>19:57</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2290,17 +2301,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119537753</v>
+        <v>119536649</v>
       </c>
       <c r="B17" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2313,37 +2324,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574485</v>
+        <v>574271</v>
       </c>
       <c r="R17" t="n">
-        <v>7173191</v>
+        <v>7173023</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2367,12 +2378,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2392,17 +2413,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119536015</v>
+        <v>119537019</v>
       </c>
       <c r="B18" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2415,21 +2436,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2439,10 +2460,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574453</v>
+        <v>574304</v>
       </c>
       <c r="R18" t="n">
-        <v>7173174</v>
+        <v>7173083</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2474,7 +2495,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2484,7 +2505,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2511,10 +2532,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119536452</v>
+        <v>119537750</v>
       </c>
       <c r="B19" t="n">
-        <v>91852</v>
+        <v>90846</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2523,41 +2544,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4366</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574298</v>
+        <v>574478</v>
       </c>
       <c r="R19" t="n">
-        <v>7172996</v>
+        <v>7173200</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2581,22 +2602,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>18:54</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>18:54</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2616,17 +2627,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119537740</v>
+        <v>119536751</v>
       </c>
       <c r="B20" t="n">
-        <v>79607</v>
+        <v>78608</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2639,37 +2650,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574317</v>
+        <v>574483</v>
       </c>
       <c r="R20" t="n">
-        <v>7173030</v>
+        <v>7173213</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2693,12 +2704,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2718,17 +2739,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119535990</v>
+        <v>119536511</v>
       </c>
       <c r="B21" t="n">
-        <v>79144</v>
+        <v>90846</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2741,21 +2762,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2765,10 +2786,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574331</v>
+        <v>574477</v>
       </c>
       <c r="R21" t="n">
-        <v>7173100</v>
+        <v>7173211</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2800,7 +2821,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2810,7 +2831,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2837,10 +2858,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119536050</v>
+        <v>119536014</v>
       </c>
       <c r="B22" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2853,39 +2874,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>574276</v>
+        <v>574494</v>
       </c>
       <c r="R22" t="n">
-        <v>7173028</v>
+        <v>7173176</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2917,7 +2936,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2927,7 +2946,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2936,6 +2955,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2954,10 +2974,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119536650</v>
+        <v>119537764</v>
       </c>
       <c r="B23" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2970,37 +2990,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574299</v>
+        <v>574381</v>
       </c>
       <c r="R23" t="n">
-        <v>7173057</v>
+        <v>7173062</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3024,22 +3044,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>19:06</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>19:06</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3059,14 +3069,14 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119537020</v>
+        <v>119537017</v>
       </c>
       <c r="B24" t="n">
         <v>78526</v>
@@ -3106,10 +3116,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574470</v>
+        <v>574299</v>
       </c>
       <c r="R24" t="n">
-        <v>7173208</v>
+        <v>7173057</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3141,7 +3151,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3151,7 +3161,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3178,10 +3188,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119537018</v>
+        <v>119536242</v>
       </c>
       <c r="B25" t="n">
-        <v>78526</v>
+        <v>90067</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3190,25 +3200,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>256703</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3218,10 +3228,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574304</v>
+        <v>574298</v>
       </c>
       <c r="R25" t="n">
-        <v>7173084</v>
+        <v>7172996</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3253,7 +3263,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3263,7 +3273,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3290,10 +3300,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119537761</v>
+        <v>119535961</v>
       </c>
       <c r="B26" t="n">
-        <v>78262</v>
+        <v>87406</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3306,37 +3316,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>4412</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574382</v>
+        <v>574445</v>
       </c>
       <c r="R26" t="n">
-        <v>7173106</v>
+        <v>7173171</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3360,12 +3370,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3385,17 +3405,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119536053</v>
+        <v>119537022</v>
       </c>
       <c r="B27" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3408,36 +3428,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574455</v>
+        <v>574492</v>
       </c>
       <c r="R27" t="n">
         <v>7173175</v>
@@ -3472,7 +3487,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3482,7 +3497,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3509,10 +3524,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119537765</v>
+        <v>119537767</v>
       </c>
       <c r="B28" t="n">
-        <v>90576</v>
+        <v>78526</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3525,21 +3540,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3549,10 +3564,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574394</v>
+        <v>574395</v>
       </c>
       <c r="R28" t="n">
-        <v>7173055</v>
+        <v>7173021</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3611,10 +3626,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119536410</v>
+        <v>119537016</v>
       </c>
       <c r="B29" t="n">
-        <v>90905</v>
+        <v>78526</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3623,25 +3638,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3651,10 +3666,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574478</v>
+        <v>574275</v>
       </c>
       <c r="R29" t="n">
-        <v>7173213</v>
+        <v>7173029</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3686,7 +3701,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3696,12 +3711,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>19:57</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>S. Str</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3712,21 +3722,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3743,10 +3738,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119537017</v>
+        <v>119536288</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3755,25 +3750,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3783,10 +3778,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574299</v>
+        <v>574304</v>
       </c>
       <c r="R30" t="n">
-        <v>7173057</v>
+        <v>7173083</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3818,7 +3813,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3828,7 +3823,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3855,10 +3850,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119536051</v>
+        <v>119536410</v>
       </c>
       <c r="B31" t="n">
-        <v>57310</v>
+        <v>90905</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3867,43 +3862,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574493</v>
+        <v>574478</v>
       </c>
       <c r="R31" t="n">
-        <v>7173176</v>
+        <v>7173213</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3935,7 +3925,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3945,7 +3935,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>S. Str</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3956,6 +3951,21 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3972,10 +3982,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119536242</v>
+        <v>119537018</v>
       </c>
       <c r="B32" t="n">
-        <v>90067</v>
+        <v>78526</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3984,25 +3994,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>256703</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4012,10 +4022,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574298</v>
+        <v>574304</v>
       </c>
       <c r="R32" t="n">
-        <v>7172996</v>
+        <v>7173084</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4047,7 +4057,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4057,7 +4067,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4084,10 +4094,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119537750</v>
+        <v>119537021</v>
       </c>
       <c r="B33" t="n">
-        <v>90846</v>
+        <v>78526</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4100,37 +4110,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574478</v>
+        <v>574516</v>
       </c>
       <c r="R33" t="n">
-        <v>7173200</v>
+        <v>7173204</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4154,12 +4164,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4179,17 +4199,17 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119536396</v>
+        <v>119536704</v>
       </c>
       <c r="B34" t="n">
-        <v>79608</v>
+        <v>90954</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4202,21 +4222,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4226,10 +4241,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574301</v>
+        <v>574517</v>
       </c>
       <c r="R34" t="n">
-        <v>7173058</v>
+        <v>7173204</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4261,7 +4276,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4271,7 +4286,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4298,10 +4313,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119536704</v>
+        <v>119535990</v>
       </c>
       <c r="B35" t="n">
-        <v>90954</v>
+        <v>79144</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4314,16 +4329,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6040186</v>
+        <v>6453</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4333,10 +4353,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574517</v>
+        <v>574331</v>
       </c>
       <c r="R35" t="n">
-        <v>7173204</v>
+        <v>7173100</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4368,7 +4388,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4378,7 +4398,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4405,7 +4425,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119536014</v>
+        <v>119537753</v>
       </c>
       <c r="B36" t="n">
         <v>90562</v>
@@ -4439,22 +4459,19 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574494</v>
+        <v>574485</v>
       </c>
       <c r="R36" t="n">
-        <v>7173176</v>
+        <v>7173191</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4478,22 +4495,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>20:24</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>20:24</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4502,7 +4509,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4514,14 +4520,14 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119537773</v>
+        <v>119537746</v>
       </c>
       <c r="B37" t="n">
         <v>78526</v>
@@ -4561,10 +4567,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574368</v>
+        <v>574574</v>
       </c>
       <c r="R37" t="n">
-        <v>7172978</v>
+        <v>7173271</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4623,10 +4629,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119537019</v>
+        <v>119536651</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4639,21 +4645,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4663,10 +4669,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574304</v>
+        <v>574475</v>
       </c>
       <c r="R38" t="n">
-        <v>7173083</v>
+        <v>7173208</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4698,7 +4704,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4708,7 +4714,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4735,10 +4741,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119537021</v>
+        <v>119536015</v>
       </c>
       <c r="B39" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4751,21 +4757,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4775,10 +4781,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574516</v>
+        <v>574453</v>
       </c>
       <c r="R39" t="n">
-        <v>7173204</v>
+        <v>7173174</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4810,7 +4816,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4820,7 +4826,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4847,10 +4853,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119537769</v>
+        <v>119537744</v>
       </c>
       <c r="B40" t="n">
-        <v>78526</v>
+        <v>56522</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4859,38 +4865,47 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574386</v>
+        <v>574625</v>
       </c>
       <c r="R40" t="n">
-        <v>7173013</v>
+        <v>7173279</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4949,10 +4964,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119537022</v>
+        <v>119536050</v>
       </c>
       <c r="B41" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4965,34 +4980,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574492</v>
+        <v>574276</v>
       </c>
       <c r="R41" t="n">
-        <v>7173175</v>
+        <v>7173028</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5024,7 +5044,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5034,7 +5054,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5061,10 +5081,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119537016</v>
+        <v>119537761</v>
       </c>
       <c r="B42" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5077,37 +5097,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574275</v>
+        <v>574382</v>
       </c>
       <c r="R42" t="n">
-        <v>7173029</v>
+        <v>7173106</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5131,22 +5151,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>19:00</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>19:00</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5166,17 +5176,17 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119535961</v>
+        <v>119537740</v>
       </c>
       <c r="B43" t="n">
-        <v>87406</v>
+        <v>79607</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5189,37 +5199,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4412</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>574445</v>
+        <v>574317</v>
       </c>
       <c r="R43" t="n">
-        <v>7173171</v>
+        <v>7173030</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5243,22 +5253,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>20:30</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>20:30</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5278,17 +5278,17 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119536751</v>
+        <v>119536396</v>
       </c>
       <c r="B44" t="n">
-        <v>78608</v>
+        <v>79608</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5301,21 +5301,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5325,10 +5325,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>574483</v>
+        <v>574301</v>
       </c>
       <c r="R44" t="n">
-        <v>7173213</v>
+        <v>7173058</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5360,7 +5360,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 30573-2024 artfynd.xlsx
+++ b/artfynd/A 30573-2024 artfynd.xlsx
@@ -1330,10 +1330,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119536051</v>
+        <v>119536452</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>91852</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,43 +1342,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574493</v>
+        <v>574298</v>
       </c>
       <c r="R8" t="n">
-        <v>7173176</v>
+        <v>7172996</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1410,7 +1405,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1420,7 +1415,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1559,10 +1554,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119536452</v>
+        <v>119536051</v>
       </c>
       <c r="B10" t="n">
-        <v>91852</v>
+        <v>57310</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,38 +1566,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574298</v>
+        <v>574493</v>
       </c>
       <c r="R10" t="n">
-        <v>7172996</v>
+        <v>7173176</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1773,7 +1773,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119537020</v>
+        <v>119537773</v>
       </c>
       <c r="B12" t="n">
         <v>78526</v>
@@ -1809,17 +1809,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574470</v>
+        <v>574368</v>
       </c>
       <c r="R12" t="n">
-        <v>7173208</v>
+        <v>7172978</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1843,22 +1843,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>19:53</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>19:53</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1878,17 +1868,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119536053</v>
+        <v>119537748</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1901,42 +1891,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574455</v>
+        <v>574478</v>
       </c>
       <c r="R13" t="n">
-        <v>7173175</v>
+        <v>7173200</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1960,22 +1945,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>20:27</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>20:27</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1995,14 +1970,14 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119537773</v>
+        <v>119537769</v>
       </c>
       <c r="B14" t="n">
         <v>78526</v>
@@ -2042,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574368</v>
+        <v>574386</v>
       </c>
       <c r="R14" t="n">
-        <v>7172978</v>
+        <v>7173013</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2104,7 +2079,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119537748</v>
+        <v>119537020</v>
       </c>
       <c r="B15" t="n">
         <v>78526</v>
@@ -2140,17 +2115,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574478</v>
+        <v>574470</v>
       </c>
       <c r="R15" t="n">
-        <v>7173200</v>
+        <v>7173208</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2174,12 +2149,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2199,17 +2184,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119537769</v>
+        <v>119536649</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2222,37 +2207,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574386</v>
+        <v>574271</v>
       </c>
       <c r="R16" t="n">
-        <v>7173013</v>
+        <v>7173023</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2276,12 +2261,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2301,17 +2296,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119536649</v>
+        <v>119536053</v>
       </c>
       <c r="B17" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2324,34 +2319,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574271</v>
+        <v>574455</v>
       </c>
       <c r="R17" t="n">
-        <v>7173023</v>
+        <v>7173175</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2532,7 +2532,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119537750</v>
+        <v>119536511</v>
       </c>
       <c r="B19" t="n">
         <v>90846</v>
@@ -2568,17 +2568,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574478</v>
+        <v>574477</v>
       </c>
       <c r="R19" t="n">
-        <v>7173200</v>
+        <v>7173211</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2602,12 +2602,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2627,17 +2637,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119536751</v>
+        <v>119537750</v>
       </c>
       <c r="B20" t="n">
-        <v>78608</v>
+        <v>90846</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2650,37 +2660,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574483</v>
+        <v>574478</v>
       </c>
       <c r="R20" t="n">
-        <v>7173213</v>
+        <v>7173200</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2704,22 +2714,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>20:07</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>20:07</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2739,17 +2739,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119536511</v>
+        <v>119536751</v>
       </c>
       <c r="B21" t="n">
-        <v>90846</v>
+        <v>78608</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2762,21 +2762,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>864</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574477</v>
+        <v>574483</v>
       </c>
       <c r="R21" t="n">
-        <v>7173211</v>
+        <v>7173213</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3188,10 +3188,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119536242</v>
+        <v>119535961</v>
       </c>
       <c r="B25" t="n">
-        <v>90067</v>
+        <v>87406</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3200,25 +3200,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>256703</v>
+        <v>4412</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574298</v>
+        <v>574445</v>
       </c>
       <c r="R25" t="n">
-        <v>7172996</v>
+        <v>7173171</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3300,10 +3300,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119535961</v>
+        <v>119536242</v>
       </c>
       <c r="B26" t="n">
-        <v>87406</v>
+        <v>90067</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3312,25 +3312,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4412</v>
+        <v>256703</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574445</v>
+        <v>574298</v>
       </c>
       <c r="R26" t="n">
-        <v>7173171</v>
+        <v>7172996</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3412,7 +3412,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119537022</v>
+        <v>119537767</v>
       </c>
       <c r="B27" t="n">
         <v>78526</v>
@@ -3448,17 +3448,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574492</v>
+        <v>574395</v>
       </c>
       <c r="R27" t="n">
-        <v>7173175</v>
+        <v>7173021</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3482,22 +3482,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>20:24</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>20:24</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3517,14 +3507,14 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119537767</v>
+        <v>119537022</v>
       </c>
       <c r="B28" t="n">
         <v>78526</v>
@@ -3560,17 +3550,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574395</v>
+        <v>574492</v>
       </c>
       <c r="R28" t="n">
-        <v>7173021</v>
+        <v>7173175</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3594,12 +3584,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4527,10 +4527,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119537746</v>
+        <v>119536651</v>
       </c>
       <c r="B37" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4543,37 +4543,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574574</v>
+        <v>574475</v>
       </c>
       <c r="R37" t="n">
-        <v>7173271</v>
+        <v>7173208</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4597,12 +4597,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4622,17 +4632,17 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119536651</v>
+        <v>119537746</v>
       </c>
       <c r="B38" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4645,37 +4655,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574475</v>
+        <v>574574</v>
       </c>
       <c r="R38" t="n">
-        <v>7173208</v>
+        <v>7173271</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4699,22 +4709,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>19:53</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>19:53</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5081,10 +5081,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119537761</v>
+        <v>119536396</v>
       </c>
       <c r="B42" t="n">
-        <v>78262</v>
+        <v>79608</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5097,37 +5097,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574382</v>
+        <v>574301</v>
       </c>
       <c r="R42" t="n">
-        <v>7173106</v>
+        <v>7173058</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5151,12 +5151,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5176,17 +5186,17 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119537740</v>
+        <v>119537761</v>
       </c>
       <c r="B43" t="n">
-        <v>79607</v>
+        <v>78262</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5199,21 +5209,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5223,10 +5233,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>574317</v>
+        <v>574382</v>
       </c>
       <c r="R43" t="n">
-        <v>7173030</v>
+        <v>7173106</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5285,10 +5295,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119536396</v>
+        <v>119537740</v>
       </c>
       <c r="B44" t="n">
-        <v>79608</v>
+        <v>79607</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5301,37 +5311,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>574301</v>
+        <v>574317</v>
       </c>
       <c r="R44" t="n">
-        <v>7173058</v>
+        <v>7173030</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5355,22 +5365,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>19:06</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>19:06</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>

--- a/artfynd/A 30573-2024 artfynd.xlsx
+++ b/artfynd/A 30573-2024 artfynd.xlsx
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119537771</v>
+        <v>119537765</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>90576</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,21 +1030,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574350</v>
+        <v>574394</v>
       </c>
       <c r="R5" t="n">
-        <v>7173009</v>
+        <v>7173055</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119537741</v>
+        <v>119536050</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,37 +1132,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574317</v>
+        <v>574276</v>
       </c>
       <c r="R6" t="n">
-        <v>7173030</v>
+        <v>7173028</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1186,12 +1191,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1211,17 +1226,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119536650</v>
+        <v>119537755</v>
       </c>
       <c r="B7" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1234,37 +1249,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574299</v>
+        <v>574478</v>
       </c>
       <c r="R7" t="n">
-        <v>7173057</v>
+        <v>7173200</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1288,22 +1303,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>19:06</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>19:06</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1323,17 +1328,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119536452</v>
+        <v>119537764</v>
       </c>
       <c r="B8" t="n">
-        <v>91852</v>
+        <v>78526</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,41 +1347,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574298</v>
+        <v>574381</v>
       </c>
       <c r="R8" t="n">
-        <v>7172996</v>
+        <v>7173062</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1400,22 +1405,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>18:54</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>18:54</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1435,17 +1430,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119536013</v>
+        <v>119537018</v>
       </c>
       <c r="B9" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,21 +1453,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1482,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574482</v>
+        <v>574304</v>
       </c>
       <c r="R9" t="n">
-        <v>7173212</v>
+        <v>7173084</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1517,7 +1512,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1527,7 +1522,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1554,10 +1549,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119536051</v>
+        <v>119536650</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1570,39 +1565,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574493</v>
+        <v>574299</v>
       </c>
       <c r="R10" t="n">
-        <v>7173176</v>
+        <v>7173057</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1634,7 +1624,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1644,7 +1634,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,10 +1661,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119537765</v>
+        <v>119536288</v>
       </c>
       <c r="B11" t="n">
-        <v>90576</v>
+        <v>79636</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1683,41 +1673,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574394</v>
+        <v>574304</v>
       </c>
       <c r="R11" t="n">
-        <v>7173055</v>
+        <v>7173083</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1741,12 +1731,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1766,17 +1766,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119537773</v>
+        <v>119536051</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1789,37 +1789,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574368</v>
+        <v>574493</v>
       </c>
       <c r="R12" t="n">
-        <v>7172978</v>
+        <v>7173176</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1843,12 +1848,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1868,17 +1883,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119537748</v>
+        <v>119536704</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>90954</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1891,37 +1906,32 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574478</v>
+        <v>574517</v>
       </c>
       <c r="R13" t="n">
-        <v>7173200</v>
+        <v>7173204</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1945,12 +1955,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1970,14 +1990,14 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119537769</v>
+        <v>119537741</v>
       </c>
       <c r="B14" t="n">
         <v>78526</v>
@@ -2017,10 +2037,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574386</v>
+        <v>574317</v>
       </c>
       <c r="R14" t="n">
-        <v>7173013</v>
+        <v>7173030</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2079,10 +2099,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119537020</v>
+        <v>119537750</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>90846</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2095,37 +2115,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574470</v>
+        <v>574478</v>
       </c>
       <c r="R15" t="n">
-        <v>7173208</v>
+        <v>7173200</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2149,22 +2169,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>19:53</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>19:53</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2184,17 +2194,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119536649</v>
+        <v>119536410</v>
       </c>
       <c r="B16" t="n">
-        <v>79607</v>
+        <v>90905</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2203,25 +2213,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>2062</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2231,10 +2241,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574271</v>
+        <v>574478</v>
       </c>
       <c r="R16" t="n">
-        <v>7173023</v>
+        <v>7173213</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2266,7 +2276,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2276,7 +2286,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>S. Str</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2287,6 +2302,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2303,10 +2333,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119536053</v>
+        <v>119535961</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>87406</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2319,39 +2349,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574455</v>
+        <v>574445</v>
       </c>
       <c r="R17" t="n">
-        <v>7173175</v>
+        <v>7173171</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2383,7 +2408,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2393,7 +2418,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2420,7 +2445,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119537019</v>
+        <v>119537016</v>
       </c>
       <c r="B18" t="n">
         <v>78526</v>
@@ -2460,10 +2485,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574304</v>
+        <v>574275</v>
       </c>
       <c r="R18" t="n">
-        <v>7173083</v>
+        <v>7173029</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2495,7 +2520,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2505,7 +2530,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2532,10 +2557,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119536511</v>
+        <v>119537773</v>
       </c>
       <c r="B19" t="n">
-        <v>90846</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2548,37 +2573,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574477</v>
+        <v>574368</v>
       </c>
       <c r="R19" t="n">
-        <v>7173211</v>
+        <v>7172978</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2602,22 +2627,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>19:57</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>19:57</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2637,17 +2652,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119537750</v>
+        <v>119537761</v>
       </c>
       <c r="B20" t="n">
-        <v>90846</v>
+        <v>78262</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2660,21 +2675,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2684,10 +2699,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574478</v>
+        <v>574382</v>
       </c>
       <c r="R20" t="n">
-        <v>7173200</v>
+        <v>7173106</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2746,10 +2761,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119536751</v>
+        <v>119537017</v>
       </c>
       <c r="B21" t="n">
-        <v>78608</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2762,21 +2777,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2786,10 +2801,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574483</v>
+        <v>574299</v>
       </c>
       <c r="R21" t="n">
-        <v>7173213</v>
+        <v>7173057</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2821,7 +2836,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2831,7 +2846,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2858,10 +2873,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119536014</v>
+        <v>119537020</v>
       </c>
       <c r="B22" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2874,37 +2889,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>574494</v>
+        <v>574470</v>
       </c>
       <c r="R22" t="n">
-        <v>7173176</v>
+        <v>7173208</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2936,7 +2948,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2946,7 +2958,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2955,7 +2967,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2974,10 +2985,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119537764</v>
+        <v>119536452</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>91852</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2986,41 +2997,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574381</v>
+        <v>574298</v>
       </c>
       <c r="R23" t="n">
-        <v>7173062</v>
+        <v>7172996</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3044,12 +3055,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3069,17 +3090,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119537017</v>
+        <v>119537740</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3092,37 +3113,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574299</v>
+        <v>574317</v>
       </c>
       <c r="R24" t="n">
-        <v>7173057</v>
+        <v>7173030</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3146,22 +3167,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>19:06</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>19:06</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3181,17 +3192,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119535961</v>
+        <v>119536651</v>
       </c>
       <c r="B25" t="n">
-        <v>87406</v>
+        <v>79607</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3204,21 +3215,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4412</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3228,10 +3239,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574445</v>
+        <v>574475</v>
       </c>
       <c r="R25" t="n">
-        <v>7173171</v>
+        <v>7173208</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3263,7 +3274,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3273,7 +3284,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3300,10 +3311,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119536242</v>
+        <v>119537744</v>
       </c>
       <c r="B26" t="n">
-        <v>90067</v>
+        <v>56522</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3316,37 +3327,46 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>256703</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574298</v>
+        <v>574625</v>
       </c>
       <c r="R26" t="n">
-        <v>7172996</v>
+        <v>7173279</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3370,22 +3390,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>18:54</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>18:54</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3405,14 +3415,14 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119537767</v>
+        <v>119537022</v>
       </c>
       <c r="B27" t="n">
         <v>78526</v>
@@ -3448,17 +3458,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574395</v>
+        <v>574492</v>
       </c>
       <c r="R27" t="n">
-        <v>7173021</v>
+        <v>7173175</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3482,12 +3492,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3507,14 +3527,14 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119537022</v>
+        <v>119537771</v>
       </c>
       <c r="B28" t="n">
         <v>78526</v>
@@ -3550,17 +3570,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574492</v>
+        <v>574350</v>
       </c>
       <c r="R28" t="n">
-        <v>7173175</v>
+        <v>7173009</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3584,22 +3604,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>20:24</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>20:24</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3619,17 +3629,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119537016</v>
+        <v>119536511</v>
       </c>
       <c r="B29" t="n">
-        <v>78526</v>
+        <v>90846</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3642,21 +3652,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3666,10 +3676,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574275</v>
+        <v>574477</v>
       </c>
       <c r="R29" t="n">
-        <v>7173029</v>
+        <v>7173211</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3701,7 +3711,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3711,7 +3721,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3738,10 +3748,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119536288</v>
+        <v>119537746</v>
       </c>
       <c r="B30" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3750,41 +3760,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574304</v>
+        <v>574574</v>
       </c>
       <c r="R30" t="n">
-        <v>7173083</v>
+        <v>7173271</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3808,22 +3818,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>19:08</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>19:08</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3843,17 +3843,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119536410</v>
+        <v>119536053</v>
       </c>
       <c r="B31" t="n">
-        <v>90905</v>
+        <v>57310</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3862,38 +3862,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574478</v>
+        <v>574455</v>
       </c>
       <c r="R31" t="n">
-        <v>7173213</v>
+        <v>7173175</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3925,7 +3930,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3935,12 +3940,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>19:57</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>S. Str</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3951,21 +3951,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3982,10 +3967,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119537018</v>
+        <v>119536014</v>
       </c>
       <c r="B32" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3998,34 +3983,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574304</v>
+        <v>574494</v>
       </c>
       <c r="R32" t="n">
-        <v>7173084</v>
+        <v>7173176</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4057,7 +4045,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4067,7 +4055,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4076,6 +4064,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4094,10 +4083,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119537021</v>
+        <v>119536242</v>
       </c>
       <c r="B33" t="n">
-        <v>78526</v>
+        <v>90067</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4106,25 +4095,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>256703</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4134,10 +4123,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574516</v>
+        <v>574298</v>
       </c>
       <c r="R33" t="n">
-        <v>7173204</v>
+        <v>7172996</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4169,7 +4158,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4179,7 +4168,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4206,10 +4195,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119536704</v>
+        <v>119536396</v>
       </c>
       <c r="B34" t="n">
-        <v>90954</v>
+        <v>79608</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4222,16 +4211,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6040186</v>
+        <v>2081</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4241,10 +4235,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574517</v>
+        <v>574301</v>
       </c>
       <c r="R34" t="n">
-        <v>7173204</v>
+        <v>7173058</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4276,7 +4270,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4286,7 +4280,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4313,10 +4307,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119535990</v>
+        <v>119537753</v>
       </c>
       <c r="B35" t="n">
-        <v>79144</v>
+        <v>90562</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4329,37 +4323,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574331</v>
+        <v>574485</v>
       </c>
       <c r="R35" t="n">
-        <v>7173100</v>
+        <v>7173191</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4383,22 +4377,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>19:17</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>19:17</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4418,17 +4402,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119537753</v>
+        <v>119535990</v>
       </c>
       <c r="B36" t="n">
-        <v>90562</v>
+        <v>79144</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4441,37 +4425,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574485</v>
+        <v>574331</v>
       </c>
       <c r="R36" t="n">
-        <v>7173191</v>
+        <v>7173100</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4495,12 +4479,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4520,17 +4514,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119536651</v>
+        <v>119536751</v>
       </c>
       <c r="B37" t="n">
-        <v>79607</v>
+        <v>78608</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4543,21 +4537,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4567,10 +4561,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574475</v>
+        <v>574483</v>
       </c>
       <c r="R37" t="n">
-        <v>7173208</v>
+        <v>7173213</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4602,7 +4596,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4612,7 +4606,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4639,7 +4633,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119537746</v>
+        <v>119537769</v>
       </c>
       <c r="B38" t="n">
         <v>78526</v>
@@ -4679,10 +4673,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574574</v>
+        <v>574386</v>
       </c>
       <c r="R38" t="n">
-        <v>7173271</v>
+        <v>7173013</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4741,7 +4735,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119536015</v>
+        <v>119536013</v>
       </c>
       <c r="B39" t="n">
         <v>90562</v>
@@ -4781,10 +4775,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574453</v>
+        <v>574482</v>
       </c>
       <c r="R39" t="n">
-        <v>7173174</v>
+        <v>7173212</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4816,7 +4810,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4826,7 +4820,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4853,10 +4847,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119537744</v>
+        <v>119536649</v>
       </c>
       <c r="B40" t="n">
-        <v>56522</v>
+        <v>79607</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4865,50 +4859,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Vilhelmina, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574625</v>
+        <v>574271</v>
       </c>
       <c r="R40" t="n">
-        <v>7173279</v>
+        <v>7173023</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4932,12 +4917,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4957,17 +4952,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119536050</v>
+        <v>119537767</v>
       </c>
       <c r="B41" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4980,42 +4975,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574276</v>
+        <v>574395</v>
       </c>
       <c r="R41" t="n">
-        <v>7173028</v>
+        <v>7173021</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5039,22 +5029,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>19:00</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>19:00</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5074,17 +5054,17 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119536396</v>
+        <v>119537021</v>
       </c>
       <c r="B42" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5097,21 +5077,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5121,10 +5101,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574301</v>
+        <v>574516</v>
       </c>
       <c r="R42" t="n">
-        <v>7173058</v>
+        <v>7173204</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5156,7 +5136,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5166,7 +5146,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5193,10 +5173,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119537761</v>
+        <v>119537019</v>
       </c>
       <c r="B43" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5209,37 +5189,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>574382</v>
+        <v>574304</v>
       </c>
       <c r="R43" t="n">
-        <v>7173106</v>
+        <v>7173083</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5263,12 +5243,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5288,17 +5278,17 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119537740</v>
+        <v>119536015</v>
       </c>
       <c r="B44" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5311,37 +5301,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>574317</v>
+        <v>574453</v>
       </c>
       <c r="R44" t="n">
-        <v>7173030</v>
+        <v>7173174</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5365,12 +5355,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>

--- a/artfynd/A 30573-2024 artfynd.xlsx
+++ b/artfynd/A 30573-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5395,6 +5395,637 @@
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>118753340</v>
+      </c>
+      <c r="B45" t="n">
+        <v>90797</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Vilhelmina, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>574381</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7173106</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Louise Karlsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Louise Karlsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>118752989</v>
+      </c>
+      <c r="B46" t="n">
+        <v>78646</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Vilhelmina, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>574381</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7173106</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Louise Karlsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Louise Karlsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>118755595</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79726</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Vilhelmina, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>574298</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7173055</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Louise Karlsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Louise Karlsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>118755013</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79726</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Vilhelmina, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>574518</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7173188</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Louise Karlsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Louise Karlsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>118755675</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79726</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Vilhelmina, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>574263</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7173022</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Louise Karlsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Louise Karlsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>118754580</v>
+      </c>
+      <c r="B50" t="n">
+        <v>78646</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Vilhelmina, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>574518</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7173188</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Louise Karlsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Louise Karlsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30573-2024 artfynd.xlsx
+++ b/artfynd/A 30573-2024 artfynd.xlsx
@@ -5397,10 +5397,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118753340</v>
+        <v>118753407</v>
       </c>
       <c r="B45" t="n">
-        <v>90797</v>
+        <v>78647</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5413,21 +5413,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>230405</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5499,10 +5499,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118752989</v>
+        <v>118754580</v>
       </c>
       <c r="B46" t="n">
-        <v>78646</v>
+        <v>78647</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5539,10 +5539,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574381</v>
+        <v>574518</v>
       </c>
       <c r="R46" t="n">
-        <v>7173106</v>
+        <v>7173188</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5604,7 +5604,7 @@
         <v>118755595</v>
       </c>
       <c r="B47" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>118755013</v>
       </c>
       <c r="B48" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5805,10 +5805,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118755675</v>
+        <v>118753340</v>
       </c>
       <c r="B49" t="n">
-        <v>79726</v>
+        <v>90807</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5821,40 +5821,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574263</v>
+        <v>574381</v>
       </c>
       <c r="R49" t="n">
-        <v>7173022</v>
+        <v>7173106</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5892,24 +5889,8 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5926,10 +5907,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118754580</v>
+        <v>118755675</v>
       </c>
       <c r="B50" t="n">
-        <v>78646</v>
+        <v>79727</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5942,37 +5923,40 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>230405</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574518</v>
+        <v>574263</v>
       </c>
       <c r="R50" t="n">
-        <v>7173188</v>
+        <v>7173022</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6010,8 +5994,24 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 30573-2024 artfynd.xlsx
+++ b/artfynd/A 30573-2024 artfynd.xlsx
@@ -5397,7 +5397,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118753407</v>
+        <v>118752989</v>
       </c>
       <c r="B45" t="n">
         <v>78647</v>
@@ -5499,7 +5499,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118754580</v>
+        <v>118754133</v>
       </c>
       <c r="B46" t="n">
         <v>78647</v>
@@ -5601,10 +5601,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118755595</v>
+        <v>118753340</v>
       </c>
       <c r="B47" t="n">
-        <v>79727</v>
+        <v>90807</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5617,21 +5617,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5641,13 +5641,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574298</v>
+        <v>574381</v>
       </c>
       <c r="R47" t="n">
-        <v>7173055</v>
+        <v>7173106</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5805,10 +5805,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118753340</v>
+        <v>118755675</v>
       </c>
       <c r="B49" t="n">
-        <v>90807</v>
+        <v>79727</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5821,37 +5821,40 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574381</v>
+        <v>574263</v>
       </c>
       <c r="R49" t="n">
-        <v>7173106</v>
+        <v>7173022</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5889,8 +5892,24 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5907,7 +5926,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118755675</v>
+        <v>118755595</v>
       </c>
       <c r="B50" t="n">
         <v>79727</v>
@@ -5941,19 +5960,16 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574263</v>
+        <v>574298</v>
       </c>
       <c r="R50" t="n">
-        <v>7173022</v>
+        <v>7173055</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5994,24 +6010,8 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 30573-2024 artfynd.xlsx
+++ b/artfynd/A 30573-2024 artfynd.xlsx
@@ -5397,10 +5397,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118752989</v>
+        <v>118753340</v>
       </c>
       <c r="B45" t="n">
-        <v>78647</v>
+        <v>90819</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5413,21 +5413,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>230405</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5502,7 +5502,7 @@
         <v>118754133</v>
       </c>
       <c r="B46" t="n">
-        <v>78647</v>
+        <v>78652</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5601,10 +5601,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118753340</v>
+        <v>118753407</v>
       </c>
       <c r="B47" t="n">
-        <v>90807</v>
+        <v>78652</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5617,21 +5617,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>230405</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5703,10 +5703,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118755013</v>
+        <v>118755595</v>
       </c>
       <c r="B48" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5743,13 +5743,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574518</v>
+        <v>574298</v>
       </c>
       <c r="R48" t="n">
-        <v>7173188</v>
+        <v>7173055</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>118755675</v>
       </c>
       <c r="B49" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5926,10 +5926,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118755595</v>
+        <v>118755013</v>
       </c>
       <c r="B50" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5966,13 +5966,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574298</v>
+        <v>574518</v>
       </c>
       <c r="R50" t="n">
-        <v>7173055</v>
+        <v>7173188</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>

--- a/artfynd/A 30573-2024 artfynd.xlsx
+++ b/artfynd/A 30573-2024 artfynd.xlsx
@@ -5397,10 +5397,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118753340</v>
+        <v>118755013</v>
       </c>
       <c r="B45" t="n">
-        <v>90819</v>
+        <v>79732</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5413,21 +5413,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574381</v>
+        <v>574518</v>
       </c>
       <c r="R45" t="n">
-        <v>7173106</v>
+        <v>7173188</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5499,10 +5499,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118754133</v>
+        <v>118755595</v>
       </c>
       <c r="B46" t="n">
-        <v>78652</v>
+        <v>79732</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5515,21 +5515,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>230405</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5539,13 +5539,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574518</v>
+        <v>574298</v>
       </c>
       <c r="R46" t="n">
-        <v>7173188</v>
+        <v>7173055</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5703,10 +5703,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118755595</v>
+        <v>118753340</v>
       </c>
       <c r="B48" t="n">
-        <v>79732</v>
+        <v>90826</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5719,21 +5719,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5743,13 +5743,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574298</v>
+        <v>574381</v>
       </c>
       <c r="R48" t="n">
-        <v>7173055</v>
+        <v>7173106</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5805,10 +5805,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118755675</v>
+        <v>118754580</v>
       </c>
       <c r="B49" t="n">
-        <v>79732</v>
+        <v>78652</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5821,40 +5821,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>230405</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574263</v>
+        <v>574518</v>
       </c>
       <c r="R49" t="n">
-        <v>7173022</v>
+        <v>7173188</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5892,24 +5889,8 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5926,7 +5907,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118755013</v>
+        <v>118755675</v>
       </c>
       <c r="B50" t="n">
         <v>79732</v>
@@ -5960,19 +5941,22 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574518</v>
+        <v>574263</v>
       </c>
       <c r="R50" t="n">
-        <v>7173188</v>
+        <v>7173022</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6010,8 +5994,24 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 30573-2024 artfynd.xlsx
+++ b/artfynd/A 30573-2024 artfynd.xlsx
@@ -5397,10 +5397,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118755013</v>
+        <v>118755595</v>
       </c>
       <c r="B45" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5415,11 +5415,6 @@
       <c r="E45" t="n">
         <v>6458</v>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -5437,13 +5432,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574518</v>
+        <v>574298</v>
       </c>
       <c r="R45" t="n">
-        <v>7173188</v>
+        <v>7173055</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5499,10 +5494,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118755595</v>
+        <v>118752989</v>
       </c>
       <c r="B46" t="n">
-        <v>79732</v>
+        <v>78653</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5515,21 +5510,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>230405</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5539,13 +5529,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574298</v>
+        <v>574381</v>
       </c>
       <c r="R46" t="n">
-        <v>7173055</v>
+        <v>7173106</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5601,10 +5591,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118753407</v>
+        <v>118753340</v>
       </c>
       <c r="B47" t="n">
-        <v>78652</v>
+        <v>90831</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5617,21 +5607,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>230405</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5703,10 +5688,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118753340</v>
+        <v>118755675</v>
       </c>
       <c r="B48" t="n">
-        <v>90826</v>
+        <v>79733</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5719,37 +5704,35 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574381</v>
+        <v>574263</v>
       </c>
       <c r="R48" t="n">
-        <v>7173106</v>
+        <v>7173022</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5787,8 +5770,19 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5805,10 +5799,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118754580</v>
+        <v>118754133</v>
       </c>
       <c r="B49" t="n">
-        <v>78652</v>
+        <v>78653</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5822,11 +5816,6 @@
       </c>
       <c r="E49" t="n">
         <v>230405</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
-        </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -5907,10 +5896,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118755675</v>
+        <v>118755013</v>
       </c>
       <c r="B50" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5925,11 +5914,6 @@
       <c r="E50" t="n">
         <v>6458</v>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
       <c r="G50" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -5941,22 +5925,19 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574263</v>
+        <v>574518</v>
       </c>
       <c r="R50" t="n">
-        <v>7173022</v>
+        <v>7173188</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5994,24 +5975,8 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 30573-2024 artfynd.xlsx
+++ b/artfynd/A 30573-2024 artfynd.xlsx
@@ -5799,10 +5799,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118754133</v>
+        <v>118755013</v>
       </c>
       <c r="B49" t="n">
-        <v>78653</v>
+        <v>79733</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5815,16 +5815,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>230405</v>
+        <v>6458</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5896,10 +5896,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118755013</v>
+        <v>118754133</v>
       </c>
       <c r="B50" t="n">
-        <v>79733</v>
+        <v>78653</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5912,16 +5912,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>230405</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>

--- a/artfynd/A 30573-2024 artfynd.xlsx
+++ b/artfynd/A 30573-2024 artfynd.xlsx
@@ -5400,7 +5400,7 @@
         <v>118755595</v>
       </c>
       <c r="B45" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5414,6 +5414,11 @@
       </c>
       <c r="E45" t="n">
         <v>6458</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -5494,10 +5499,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118752989</v>
+        <v>118755013</v>
       </c>
       <c r="B46" t="n">
-        <v>78653</v>
+        <v>79737</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5510,16 +5515,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>230405</v>
+        <v>6458</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5529,10 +5539,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574381</v>
+        <v>574518</v>
       </c>
       <c r="R46" t="n">
-        <v>7173106</v>
+        <v>7173188</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5591,10 +5601,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118753340</v>
+        <v>118754133</v>
       </c>
       <c r="B47" t="n">
-        <v>90831</v>
+        <v>78657</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5607,16 +5617,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>230405</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5626,10 +5641,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574381</v>
+        <v>574518</v>
       </c>
       <c r="R47" t="n">
-        <v>7173106</v>
+        <v>7173188</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5688,10 +5703,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118755675</v>
+        <v>118753407</v>
       </c>
       <c r="B48" t="n">
-        <v>79733</v>
+        <v>78657</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5704,35 +5719,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>230405</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574263</v>
+        <v>574381</v>
       </c>
       <c r="R48" t="n">
-        <v>7173022</v>
+        <v>7173106</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5770,19 +5787,8 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5799,10 +5805,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118755013</v>
+        <v>118755675</v>
       </c>
       <c r="B49" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5817,6 +5823,11 @@
       <c r="E49" t="n">
         <v>6458</v>
       </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -5828,19 +5839,22 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574518</v>
+        <v>574263</v>
       </c>
       <c r="R49" t="n">
-        <v>7173188</v>
+        <v>7173022</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5878,8 +5892,24 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5896,10 +5926,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118754133</v>
+        <v>118753340</v>
       </c>
       <c r="B50" t="n">
-        <v>78653</v>
+        <v>90844</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5912,16 +5942,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>230405</v>
+        <v>5432</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5931,10 +5966,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574518</v>
+        <v>574381</v>
       </c>
       <c r="R50" t="n">
-        <v>7173188</v>
+        <v>7173106</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 30573-2024 artfynd.xlsx
+++ b/artfynd/A 30573-2024 artfynd.xlsx
@@ -5397,10 +5397,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118755595</v>
+        <v>118754133</v>
       </c>
       <c r="B45" t="n">
-        <v>79737</v>
+        <v>78657</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5413,21 +5413,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>230405</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5437,13 +5437,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574298</v>
+        <v>574518</v>
       </c>
       <c r="R45" t="n">
-        <v>7173055</v>
+        <v>7173188</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118755013</v>
+        <v>118755675</v>
       </c>
       <c r="B46" t="n">
         <v>79737</v>
@@ -5533,19 +5533,22 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574518</v>
+        <v>574263</v>
       </c>
       <c r="R46" t="n">
-        <v>7173188</v>
+        <v>7173022</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5583,8 +5586,24 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5601,7 +5620,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118754133</v>
+        <v>118752989</v>
       </c>
       <c r="B47" t="n">
         <v>78657</v>
@@ -5641,10 +5660,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574518</v>
+        <v>574381</v>
       </c>
       <c r="R47" t="n">
-        <v>7173188</v>
+        <v>7173106</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5703,10 +5722,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118753407</v>
+        <v>118753340</v>
       </c>
       <c r="B48" t="n">
-        <v>78657</v>
+        <v>90857</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5719,21 +5738,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>230405</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5805,7 +5824,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118755675</v>
+        <v>118755595</v>
       </c>
       <c r="B49" t="n">
         <v>79737</v>
@@ -5839,19 +5858,16 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574263</v>
+        <v>574298</v>
       </c>
       <c r="R49" t="n">
-        <v>7173022</v>
+        <v>7173055</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5892,24 +5908,8 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5926,10 +5926,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118753340</v>
+        <v>118755013</v>
       </c>
       <c r="B50" t="n">
-        <v>90844</v>
+        <v>79737</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5942,21 +5942,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5966,10 +5966,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574381</v>
+        <v>574518</v>
       </c>
       <c r="R50" t="n">
-        <v>7173106</v>
+        <v>7173188</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 30573-2024 artfynd.xlsx
+++ b/artfynd/A 30573-2024 artfynd.xlsx
@@ -5397,10 +5397,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118754133</v>
+        <v>118755675</v>
       </c>
       <c r="B45" t="n">
-        <v>78657</v>
+        <v>79737</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5413,37 +5413,40 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>230405</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574518</v>
+        <v>574263</v>
       </c>
       <c r="R45" t="n">
-        <v>7173188</v>
+        <v>7173022</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5481,8 +5484,24 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5499,10 +5518,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118755675</v>
+        <v>118753407</v>
       </c>
       <c r="B46" t="n">
-        <v>79737</v>
+        <v>78657</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5515,40 +5534,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>230405</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574263</v>
+        <v>574381</v>
       </c>
       <c r="R46" t="n">
-        <v>7173022</v>
+        <v>7173106</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5586,24 +5602,8 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5620,10 +5620,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118752989</v>
+        <v>118753340</v>
       </c>
       <c r="B47" t="n">
-        <v>78657</v>
+        <v>90857</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5636,21 +5636,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>230405</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5722,10 +5722,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118753340</v>
+        <v>118755013</v>
       </c>
       <c r="B48" t="n">
-        <v>90857</v>
+        <v>79737</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5738,21 +5738,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5762,10 +5762,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574381</v>
+        <v>574518</v>
       </c>
       <c r="R48" t="n">
-        <v>7173106</v>
+        <v>7173188</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5824,10 +5824,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118755595</v>
+        <v>118754133</v>
       </c>
       <c r="B49" t="n">
-        <v>79737</v>
+        <v>78657</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5840,21 +5840,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>230405</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5864,13 +5864,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574298</v>
+        <v>574518</v>
       </c>
       <c r="R49" t="n">
-        <v>7173055</v>
+        <v>7173188</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118755013</v>
+        <v>118755595</v>
       </c>
       <c r="B50" t="n">
         <v>79737</v>
@@ -5966,13 +5966,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574518</v>
+        <v>574298</v>
       </c>
       <c r="R50" t="n">
-        <v>7173188</v>
+        <v>7173055</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>

--- a/artfynd/A 30573-2024 artfynd.xlsx
+++ b/artfynd/A 30573-2024 artfynd.xlsx
@@ -5397,7 +5397,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118755675</v>
+        <v>118755013</v>
       </c>
       <c r="B45" t="n">
         <v>79737</v>
@@ -5431,22 +5431,19 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574263</v>
+        <v>574518</v>
       </c>
       <c r="R45" t="n">
-        <v>7173022</v>
+        <v>7173188</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5484,24 +5481,8 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5518,7 +5499,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118753407</v>
+        <v>118754133</v>
       </c>
       <c r="B46" t="n">
         <v>78657</v>
@@ -5558,10 +5539,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574381</v>
+        <v>574518</v>
       </c>
       <c r="R46" t="n">
-        <v>7173106</v>
+        <v>7173188</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5620,10 +5601,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118753340</v>
+        <v>118752989</v>
       </c>
       <c r="B47" t="n">
-        <v>90857</v>
+        <v>78657</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5636,21 +5617,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>230405</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5722,7 +5703,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118755013</v>
+        <v>118755595</v>
       </c>
       <c r="B48" t="n">
         <v>79737</v>
@@ -5762,13 +5743,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574518</v>
+        <v>574298</v>
       </c>
       <c r="R48" t="n">
-        <v>7173188</v>
+        <v>7173055</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5824,10 +5805,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118754133</v>
+        <v>118753340</v>
       </c>
       <c r="B49" t="n">
-        <v>78657</v>
+        <v>90851</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5840,21 +5821,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>230405</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5864,10 +5845,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574518</v>
+        <v>574381</v>
       </c>
       <c r="R49" t="n">
-        <v>7173188</v>
+        <v>7173106</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5926,7 +5907,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118755595</v>
+        <v>118755675</v>
       </c>
       <c r="B50" t="n">
         <v>79737</v>
@@ -5960,16 +5941,19 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574298</v>
+        <v>574263</v>
       </c>
       <c r="R50" t="n">
-        <v>7173055</v>
+        <v>7173022</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6010,8 +5994,24 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 30573-2024 artfynd.xlsx
+++ b/artfynd/A 30573-2024 artfynd.xlsx
@@ -5499,10 +5499,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118754133</v>
+        <v>118753340</v>
       </c>
       <c r="B46" t="n">
-        <v>78657</v>
+        <v>90851</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5515,21 +5515,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>230405</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5539,10 +5539,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574518</v>
+        <v>574381</v>
       </c>
       <c r="R46" t="n">
-        <v>7173188</v>
+        <v>7173106</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5601,7 +5601,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118752989</v>
+        <v>118754580</v>
       </c>
       <c r="B47" t="n">
         <v>78657</v>
@@ -5641,10 +5641,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574381</v>
+        <v>574518</v>
       </c>
       <c r="R47" t="n">
-        <v>7173106</v>
+        <v>7173188</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5703,10 +5703,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118755595</v>
+        <v>118753407</v>
       </c>
       <c r="B48" t="n">
-        <v>79737</v>
+        <v>78657</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5719,21 +5719,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>230405</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5743,13 +5743,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574298</v>
+        <v>574381</v>
       </c>
       <c r="R48" t="n">
-        <v>7173055</v>
+        <v>7173106</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5805,10 +5805,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118753340</v>
+        <v>118755675</v>
       </c>
       <c r="B49" t="n">
-        <v>90851</v>
+        <v>79737</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5821,37 +5821,40 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574381</v>
+        <v>574263</v>
       </c>
       <c r="R49" t="n">
-        <v>7173106</v>
+        <v>7173022</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5889,8 +5892,24 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5907,7 +5926,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118755675</v>
+        <v>118755595</v>
       </c>
       <c r="B50" t="n">
         <v>79737</v>
@@ -5941,19 +5960,16 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574263</v>
+        <v>574298</v>
       </c>
       <c r="R50" t="n">
-        <v>7173022</v>
+        <v>7173055</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5994,24 +6010,8 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 30573-2024 artfynd.xlsx
+++ b/artfynd/A 30573-2024 artfynd.xlsx
@@ -5397,10 +5397,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118755013</v>
+        <v>118754133</v>
       </c>
       <c r="B45" t="n">
-        <v>79737</v>
+        <v>78658</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5413,21 +5413,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>230405</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5499,10 +5499,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118753340</v>
+        <v>118753407</v>
       </c>
       <c r="B46" t="n">
-        <v>90851</v>
+        <v>78658</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5515,21 +5515,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>230405</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5601,10 +5601,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118754580</v>
+        <v>118753340</v>
       </c>
       <c r="B47" t="n">
-        <v>78657</v>
+        <v>90852</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5617,21 +5617,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>230405</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5641,10 +5641,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574518</v>
+        <v>574381</v>
       </c>
       <c r="R47" t="n">
-        <v>7173188</v>
+        <v>7173106</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5703,10 +5703,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118753407</v>
+        <v>118755013</v>
       </c>
       <c r="B48" t="n">
-        <v>78657</v>
+        <v>79738</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5719,21 +5719,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>230405</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5743,10 +5743,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574381</v>
+        <v>574518</v>
       </c>
       <c r="R48" t="n">
-        <v>7173106</v>
+        <v>7173188</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5805,10 +5805,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118755675</v>
+        <v>118755595</v>
       </c>
       <c r="B49" t="n">
-        <v>79737</v>
+        <v>79738</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5839,19 +5839,16 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574263</v>
+        <v>574298</v>
       </c>
       <c r="R49" t="n">
-        <v>7173022</v>
+        <v>7173055</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5892,24 +5889,8 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5926,10 +5907,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118755595</v>
+        <v>118755675</v>
       </c>
       <c r="B50" t="n">
-        <v>79737</v>
+        <v>79738</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5960,16 +5941,19 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574298</v>
+        <v>574263</v>
       </c>
       <c r="R50" t="n">
-        <v>7173055</v>
+        <v>7173022</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6010,8 +5994,24 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 30573-2024 artfynd.xlsx
+++ b/artfynd/A 30573-2024 artfynd.xlsx
@@ -5397,10 +5397,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118754133</v>
+        <v>118754580</v>
       </c>
       <c r="B45" t="n">
-        <v>78658</v>
+        <v>78661</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5499,10 +5499,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118753407</v>
+        <v>118755595</v>
       </c>
       <c r="B46" t="n">
-        <v>78658</v>
+        <v>79741</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5515,21 +5515,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>230405</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5539,13 +5539,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574381</v>
+        <v>574298</v>
       </c>
       <c r="R46" t="n">
-        <v>7173106</v>
+        <v>7173055</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5601,10 +5601,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118753340</v>
+        <v>118753407</v>
       </c>
       <c r="B47" t="n">
-        <v>90852</v>
+        <v>78661</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5617,21 +5617,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>230405</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5706,7 +5706,7 @@
         <v>118755013</v>
       </c>
       <c r="B48" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5805,10 +5805,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118755595</v>
+        <v>118753340</v>
       </c>
       <c r="B49" t="n">
-        <v>79738</v>
+        <v>90855</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5821,21 +5821,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5845,13 +5845,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574298</v>
+        <v>574381</v>
       </c>
       <c r="R49" t="n">
-        <v>7173055</v>
+        <v>7173106</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>118755675</v>
       </c>
       <c r="B50" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>

--- a/artfynd/A 30573-2024 artfynd.xlsx
+++ b/artfynd/A 30573-2024 artfynd.xlsx
@@ -5397,7 +5397,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118754580</v>
+        <v>118753407</v>
       </c>
       <c r="B45" t="n">
         <v>78661</v>
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574518</v>
+        <v>574381</v>
       </c>
       <c r="R45" t="n">
-        <v>7173188</v>
+        <v>7173106</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5601,10 +5601,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118753407</v>
+        <v>118755013</v>
       </c>
       <c r="B47" t="n">
-        <v>78661</v>
+        <v>79741</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5617,21 +5617,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>230405</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5641,10 +5641,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574381</v>
+        <v>574518</v>
       </c>
       <c r="R47" t="n">
-        <v>7173106</v>
+        <v>7173188</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5703,10 +5703,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118755013</v>
+        <v>118754133</v>
       </c>
       <c r="B48" t="n">
-        <v>79741</v>
+        <v>78661</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5719,21 +5719,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>230405</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5805,10 +5805,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118753340</v>
+        <v>118755675</v>
       </c>
       <c r="B49" t="n">
-        <v>90855</v>
+        <v>79741</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5821,37 +5821,40 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574381</v>
+        <v>574263</v>
       </c>
       <c r="R49" t="n">
-        <v>7173106</v>
+        <v>7173022</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5889,8 +5892,24 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5907,10 +5926,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118755675</v>
+        <v>118753340</v>
       </c>
       <c r="B50" t="n">
-        <v>79741</v>
+        <v>90855</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5923,40 +5942,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574263</v>
+        <v>574381</v>
       </c>
       <c r="R50" t="n">
-        <v>7173022</v>
+        <v>7173106</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5994,24 +6010,8 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
